--- a/src/nodes/LPC/compressor_stage_1_blade_stator_coordinates_foil.xlsx
+++ b/src/nodes/LPC/compressor_stage_1_blade_stator_coordinates_foil.xlsx
@@ -1023,7 +1023,7 @@
         <v>0.00097482695731704306</v>
       </c>
       <c r="B2">
-        <v>0.00052673637153346229</v>
+        <v>0.00059887356637492351</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1031,7 +1031,7 @@
         <v>0.0019496539146340861</v>
       </c>
       <c r="B3">
-        <v>0.00082051923414667841</v>
+        <v>0.00091995158379301666</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1039,7 +1039,7 @@
         <v>0.0029244808719511295</v>
       </c>
       <c r="B4">
-        <v>0.0010744011709108256</v>
+        <v>0.001194889782835212</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1047,7 +1047,7 @@
         <v>0.0038993078292681722</v>
       </c>
       <c r="B5">
-        <v>0.0012991398946597345</v>
+        <v>0.0014365904956414374</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1055,7 +1055,7 @@
         <v>0.004874134786585215</v>
       </c>
       <c r="B6">
-        <v>0.0014991365526474789</v>
+        <v>0.001650328588886831</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1063,7 +1063,7 @@
         <v>0.005848961743902259</v>
       </c>
       <c r="B7">
-        <v>0.001676912499911438</v>
+        <v>0.0018391237056089938</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1071,7 +1071,7 @@
         <v>0.0068237887012193013</v>
       </c>
       <c r="B8">
-        <v>0.0018339591782797282</v>
+        <v>0.0020047598548034017</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1079,7 +1079,7 @@
         <v>0.0077986156585363444</v>
       </c>
       <c r="B9">
-        <v>0.001972592614196798</v>
+        <v>0.0021500111204285</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1087,7 +1087,7 @@
         <v>0.0087734426158533867</v>
       </c>
       <c r="B10">
-        <v>0.0020953104947686206</v>
+        <v>0.0022778698567120725</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1095,7 +1095,7 @@
         <v>0.00974826957317043</v>
       </c>
       <c r="B11">
-        <v>0.0022045125651309382</v>
+        <v>0.002391211423996298</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1103,7 +1103,7 @@
         <v>0.010723096530487473</v>
       </c>
       <c r="B12">
-        <v>0.0023014870070405297</v>
+        <v>0.0024915775702028012</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1111,7 +1111,7 @@
         <v>0.011697923487804518</v>
       </c>
       <c r="B13">
-        <v>0.00238317369070855</v>
+        <v>0.0025752925874565923</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1119,7 +1119,7 @@
         <v>0.012672750445121559</v>
       </c>
       <c r="B14">
-        <v>0.0024477471186729895</v>
+        <v>0.0026401625940545314</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1127,7 +1127,7 @@
         <v>0.013647577402438603</v>
       </c>
       <c r="B15">
-        <v>0.0025026686343248053</v>
+        <v>0.0026951384687774822</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1135,7 +1135,7 @@
         <v>0.014622404359755644</v>
       </c>
       <c r="B16">
-        <v>0.0025547817212742815</v>
+        <v>0.0027484298900790072</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1143,7 +1143,7 @@
         <v>0.015597231317072689</v>
       </c>
       <c r="B17">
-        <v>0.0025991715831560373</v>
+        <v>0.0027941369746194459</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1151,7 +1151,7 @@
         <v>0.016572058274389734</v>
       </c>
       <c r="B18">
-        <v>0.0026294877641050308</v>
+        <v>0.0028246373490700034</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1159,7 +1159,7 @@
         <v>0.017546885231706773</v>
       </c>
       <c r="B19">
-        <v>0.0026453954502332205</v>
+        <v>0.0028395282419385608</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1167,7 +1167,7 @@
         <v>0.018521712189023817</v>
       </c>
       <c r="B20">
-        <v>0.0026480637381468175</v>
+        <v>0.0028402117821921696</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1175,7 +1175,7 @@
         <v>0.01949653914634086</v>
       </c>
       <c r="B21">
-        <v>0.0026386617244520327</v>
+        <v>0.00282809009879788</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1183,7 +1183,7 @@
         <v>0.020471366103657903</v>
       </c>
       <c r="B22">
-        <v>0.0026181498855832978</v>
+        <v>0.0028043152338541933</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1191,7 +1191,7 @@
         <v>0.021446193060974946</v>
       </c>
       <c r="B23">
-        <v>0.0025866542172879306</v>
+        <v>0.0027690388819854093</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1199,7 +1199,7 @@
         <v>0.022421020018291993</v>
       </c>
       <c r="B24">
-        <v>0.00254409209514147</v>
+        <v>0.0027221626509472772</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1207,7 +1207,7 @@
         <v>0.023395846975609036</v>
       </c>
       <c r="B25">
-        <v>0.002490380894719456</v>
+        <v>0.0026635881484955472</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1215,7 +1215,7 @@
         <v>0.024370673932926076</v>
       </c>
       <c r="B26">
-        <v>0.002425402686301923</v>
+        <v>0.0025931748654857813</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1223,7 +1223,7 @@
         <v>0.025345500890243119</v>
       </c>
       <c r="B27">
-        <v>0.0023488983189868923</v>
+        <v>0.0025106138251727896</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1231,7 +1231,7 @@
         <v>0.026320327847560162</v>
       </c>
       <c r="B28">
-        <v>0.0022605733365768819</v>
+        <v>0.0024155539339111957</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1239,7 +1239,7 @@
         <v>0.027295154804877205</v>
       </c>
       <c r="B29">
-        <v>0.0021601332828744095</v>
+        <v>0.0023076440980556241</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1247,7 +1247,7 @@
         <v>0.028269981762194252</v>
       </c>
       <c r="B30">
-        <v>0.0020474371113307229</v>
+        <v>0.0021867175721803403</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1255,7 +1255,7 @@
         <v>0.029244808719511288</v>
       </c>
       <c r="B31">
-        <v>0.0019229574139919927</v>
+        <v>0.002053345003738181</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1263,7 +1263,7 @@
         <v>0.030219635676828335</v>
       </c>
       <c r="B32">
-        <v>0.0017873201925531191</v>
+        <v>0.0019082813884016235</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1271,7 +1271,7 @@
         <v>0.031194462634145378</v>
       </c>
       <c r="B33">
-        <v>0.0016411514487090033</v>
+        <v>0.0017522817218431463</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1279,7 +1279,7 @@
         <v>0.032169289591462424</v>
       </c>
       <c r="B34">
-        <v>0.0014848261843213126</v>
+        <v>0.0015858000765763471</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1287,7 +1287,7 @@
         <v>0.033144116548779468</v>
       </c>
       <c r="B35">
-        <v>0.0013177154019187822</v>
+        <v>0.0014080868324792973</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1295,7 +1295,7 @@
         <v>0.034118943506096504</v>
       </c>
       <c r="B36">
-        <v>0.0011389391041969144</v>
+        <v>0.0012180914462711877</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1303,7 +1303,7 @@
         <v>0.035093770463413547</v>
       </c>
       <c r="B37">
-        <v>0.00094761729385120866</v>
+        <v>0.0010147633746712067</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1311,7 +1311,7 @@
         <v>0.03606859742073059</v>
       </c>
       <c r="B38">
-        <v>0.00074225630201247921</v>
+        <v>0.0007963159280120392</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1319,7 +1319,7 @@
         <v>0.037043424378047633</v>
       </c>
       <c r="B39">
-        <v>0.00051890777355278442</v>
+        <v>0.000558017831080344</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1327,7 +1327,7 @@
         <v>0.038018251335364683</v>
       </c>
       <c r="B40">
-        <v>0.00027300968177949506</v>
+        <v>0.00029440166227627377</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -1335,7 +1335,7 @@
         <v>0.03899307829268172</v>
       </c>
       <c r="B41">
-        <v>-1.7316405328618654E-17</v>
+        <v>-1.7384047536933571E-17</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -1351,7 +1351,7 @@
         <v>0.038018251335364683</v>
       </c>
       <c r="B43">
-        <v>5.9089876811706387E-05</v>
+        <v>3.7697896314927534E-05</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -1359,7 +1359,7 @@
         <v>0.037043424378047633</v>
       </c>
       <c r="B44">
-        <v>0.00012780719827718744</v>
+        <v>8.8697140749627754E-05</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -1367,7 +1367,7 @@
         <v>0.03606859742073059</v>
       </c>
       <c r="B45">
-        <v>0.00020166004201687776</v>
+        <v>0.00014760041601731764</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -1375,7 +1375,7 @@
         <v>0.035093770463413547</v>
       </c>
       <c r="B46">
-        <v>0.00027615648565122952</v>
+        <v>0.00020901040483123161</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -1383,7 +1383,7 @@
         <v>0.034118943506096504</v>
       </c>
       <c r="B47">
-        <v>0.00034741568345418361</v>
+        <v>0.00026826334137991059</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -1391,7 +1391,7 @@
         <v>0.033144116548779468</v>
       </c>
       <c r="B48">
-        <v>0.00041400109631363577</v>
+        <v>0.00032362966575312112</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -1399,7 +1399,7 @@
         <v>0.032169289591462424</v>
       </c>
       <c r="B49">
-        <v>0.00047508726177097112</v>
+        <v>0.00037411336951593703</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -1407,7 +1407,7 @@
         <v>0.031194462634145378</v>
       </c>
       <c r="B50">
-        <v>0.00052984871736757417</v>
+        <v>0.00041871844423343134</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -1415,7 +1415,7 @@
         <v>0.030219635676828335</v>
       </c>
       <c r="B51">
-        <v>0.000577708234068078</v>
+        <v>0.000456747038219574</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -1423,7 +1423,7 @@
         <v>0.029244808719511288</v>
       </c>
       <c r="B52">
-        <v>0.00061908151653011</v>
+        <v>0.00048869392678392175</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -1431,7 +1431,7 @@
         <v>0.028269981762194252</v>
       </c>
       <c r="B53">
-        <v>0.00065463250283454531</v>
+        <v>0.00051535204198492775</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -1439,7 +1439,7 @@
         <v>0.027295154804877205</v>
       </c>
       <c r="B54">
-        <v>0.00068502513106226024</v>
+        <v>0.0005375143158810455</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -1447,7 +1447,7 @@
         <v>0.026320327847560162</v>
       </c>
       <c r="B55">
-        <v>0.00071076736323374132</v>
+        <v>0.00055578676589942738</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -1455,7 +1455,7 @@
         <v>0.025345500890243119</v>
       </c>
       <c r="B56">
-        <v>0.00073174325712791919</v>
+        <v>0.000570027750942022</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -1463,7 +1463,7 @@
         <v>0.024370673932926076</v>
       </c>
       <c r="B57">
-        <v>0.00074768089446333611</v>
+        <v>0.00057990871527947743</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -1471,7 +1471,7 @@
         <v>0.023395846975609036</v>
       </c>
       <c r="B58">
-        <v>0.00075830835695853355</v>
+        <v>0.00058510110318244141</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -1479,7 +1479,7 @@
         <v>0.022421020018291993</v>
       </c>
       <c r="B59">
-        <v>0.0007633865370833909</v>
+        <v>0.00058531598127758316</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -1487,7 +1487,7 @@
         <v>0.021446193060974946</v>
       </c>
       <c r="B60">
-        <v>0.00076280757031313646</v>
+        <v>0.00058042290561565715</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -1495,7 +1495,7 @@
         <v>0.020471366103657903</v>
       </c>
       <c r="B61">
-        <v>0.00075649640287433594</v>
+        <v>0.00057033105460343981</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -1503,7 +1503,7 @@
         <v>0.01949653914634086</v>
       </c>
       <c r="B62">
-        <v>0.00074437798099355468</v>
+        <v>0.0005549496066477069</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -1511,7 +1511,7 @@
         <v>0.018521712189023817</v>
       </c>
       <c r="B63">
-        <v>0.00072658329769329606</v>
+        <v>0.00053443525364794411</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -1519,7 +1519,7 @@
         <v>0.017546885231706773</v>
       </c>
       <c r="B64">
-        <v>0.0007040675331798147</v>
+        <v>0.00050993474147447413</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -1527,7 +1527,7 @@
         <v>0.016572058274389734</v>
       </c>
       <c r="B65">
-        <v>0.00067799191445530257</v>
+        <v>0.0004828423294903297</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -1535,7 +1535,7 @@
         <v>0.015597231317072689</v>
       </c>
       <c r="B66">
-        <v>0.00064951766852195151</v>
+        <v>0.000454552277058543</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -1543,7 +1543,7 @@
         <v>0.014622404359755644</v>
       </c>
       <c r="B67">
-        <v>0.00061830003322702054</v>
+        <v>0.00042465186442229466</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -1551,7 +1551,7 @@
         <v>0.013647577402438603</v>
       </c>
       <c r="B68">
-        <v>0.00057797028979803553</v>
+        <v>0.00038550045534535874</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -1559,7 +1559,7 @@
         <v>0.012672750445121559</v>
       </c>
       <c r="B69">
-        <v>0.00052359236485756964</v>
+        <v>0.0003311768894760278</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -1567,7 +1567,7 @@
         <v>0.011697923487804518</v>
       </c>
       <c r="B70">
-        <v>0.00046198472322812114</v>
+        <v>0.00026986582648007843</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -1575,7 +1575,7 @@
         <v>0.010723096530487473</v>
       </c>
       <c r="B71">
-        <v>0.00040058137541781208</v>
+        <v>0.00021049081225554044</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -1583,7 +1583,7 @@
         <v>0.00974826957317043</v>
       </c>
       <c r="B72">
-        <v>0.0003375239764773373</v>
+        <v>0.00015082511761197733</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -1591,7 +1591,7 @@
         <v>0.0087734426158533867</v>
       </c>
       <c r="B73">
-        <v>0.00026971687533410184</v>
+        <v>8.7157513390650107E-05</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -1599,7 +1599,7 @@
         <v>0.0077986156585363444</v>
       </c>
       <c r="B74">
-        <v>0.00019840755187977953</v>
+        <v>2.0989045648077771E-05</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -1607,7 +1607,7 @@
         <v>0.0068237887012193013</v>
       </c>
       <c r="B75">
-        <v>0.00012595241304299131</v>
+        <v>-4.4848263480682362E-05</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -1615,7 +1615,7 @@
         <v>0.005848961743902259</v>
       </c>
       <c r="B76">
-        <v>5.4800442935878321E-05</v>
+        <v>-0.00010741076276167766</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1623,7 +1623,7 @@
         <v>0.004874134786585215</v>
       </c>
       <c r="B77">
-        <v>-1.2783809746045704E-05</v>
+        <v>-0.0001639758459853981</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1631,7 +1631,7 @@
         <v>0.0038993078292681722</v>
       </c>
       <c r="B78">
-        <v>-7.536611515729613E-05</v>
+        <v>-0.00021281671613899907</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1639,7 +1639,7 @@
         <v>0.0029244808719511295</v>
       </c>
       <c r="B79">
-        <v>-0.00013048494833303961</v>
+        <v>-0.00025097356025742605</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1647,7 +1647,7 @@
         <v>0.0019496539146340861</v>
       </c>
       <c r="B80">
-        <v>-0.00017380426231670523</v>
+        <v>-0.00027323661196304355</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1655,7 +1655,7 @@
         <v>0.00097482695731704306</v>
       </c>
       <c r="B81">
-        <v>-0.00019463557688114945</v>
+        <v>-0.00026677277172261059</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1689,7 +1689,7 @@
         <v>0.0010567027551749218</v>
       </c>
       <c r="B2">
-        <v>0.00072494573811857034</v>
+        <v>0.00088133774588445852</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1697,7 +1697,7 @@
         <v>0.0021134055103498436</v>
       </c>
       <c r="B3">
-        <v>0.001100289629967348</v>
+        <v>0.0013158569920230319</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1705,7 +1705,7 @@
         <v>0.0031701082655247654</v>
       </c>
       <c r="B4">
-        <v>0.0014189880063129579</v>
+        <v>0.0016802049273921984</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1713,7 +1713,7 @@
         <v>0.0042268110206996872</v>
       </c>
       <c r="B5">
-        <v>0.001697350104325239</v>
+        <v>0.0019953402812845668</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1721,7 +1721,7 @@
         <v>0.0052835137758746086</v>
       </c>
       <c r="B6">
-        <v>0.001942039516979232</v>
+        <v>0.0022698208530521321</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1729,7 +1729,7 @@
         <v>0.0063402165310495308</v>
       </c>
       <c r="B7">
-        <v>0.0021568683537368711</v>
+        <v>0.0025085390306590848</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1737,7 +1737,7 @@
         <v>0.0073969192862244531</v>
       </c>
       <c r="B8">
-        <v>0.0023440863689168454</v>
+        <v>0.0027143788482406543</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1745,7 +1745,7 @@
         <v>0.0084536220413993744</v>
       </c>
       <c r="B9">
-        <v>0.0025071960670493675</v>
+        <v>0.0028918358699330385</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1753,7 +1753,7 @@
         <v>0.0095103247965742949</v>
       </c>
       <c r="B10">
-        <v>0.0026499763017272093</v>
+        <v>0.0030457613778386832</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1761,7 +1761,7 @@
         <v>0.010567027551749217</v>
       </c>
       <c r="B11">
-        <v>0.0027760585725818574</v>
+        <v>0.0031808179959240596</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1769,7 +1769,7 @@
         <v>0.011623730306924139</v>
       </c>
       <c r="B12">
-        <v>0.0028873881154237529</v>
+        <v>0.0032995006864161782</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1777,7 +1777,7 @@
         <v>0.012680433062099062</v>
       </c>
       <c r="B13">
-        <v>0.002979312464740438</v>
+        <v>0.003395822422720185</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1785,7 +1785,7 @@
         <v>0.013737135817273982</v>
       </c>
       <c r="B14">
-        <v>0.0030490534533465018</v>
+        <v>0.0034662063879218222</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1793,7 +1793,7 @@
         <v>0.014793838572448906</v>
       </c>
       <c r="B15">
-        <v>0.0031079278086876107</v>
+        <v>0.0035251985926510842</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1801,7 +1801,7 @@
         <v>0.015850541327623827</v>
       </c>
       <c r="B16">
-        <v>0.0031663151540363074</v>
+        <v>0.0035861405435058786</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1809,7 +1809,7 @@
         <v>0.016907244082798749</v>
       </c>
       <c r="B17">
-        <v>0.0032167518013415551</v>
+        <v>0.0036394329034115233</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1817,7 +1817,7 @@
         <v>0.017963946837973671</v>
       </c>
       <c r="B18">
-        <v>0.0032495960429101693</v>
+        <v>0.0036726764728385384</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1825,7 +1825,7 @@
         <v>0.01902064959314859</v>
       </c>
       <c r="B19">
-        <v>0.0032643374038039664</v>
+        <v>0.0036852134461108558</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1833,7 +1833,7 @@
         <v>0.020077352348323516</v>
       </c>
       <c r="B20">
-        <v>0.0032627482172735084</v>
+        <v>0.0036793213660157621</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1841,7 +1841,7 @@
         <v>0.021134055103498434</v>
       </c>
       <c r="B21">
-        <v>0.00324660081656936</v>
+        <v>0.0036572777753405413</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1849,7 +1849,7 @@
         <v>0.022190757858673357</v>
       </c>
       <c r="B22">
-        <v>0.0032173515478459273</v>
+        <v>0.0036209543308001022</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1857,7 +1857,7 @@
         <v>0.023247460613848279</v>
       </c>
       <c r="B23">
-        <v>0.0031751928088729832</v>
+        <v>0.0035705991448198465</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1865,7 +1865,7 @@
         <v>0.0243041633690232</v>
       </c>
       <c r="B24">
-        <v>0.0031200010103241437</v>
+        <v>0.0035060544437527995</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1873,7 +1873,7 @@
         <v>0.025360866124198123</v>
       </c>
       <c r="B25">
-        <v>0.0030516525628730244</v>
+        <v>0.0034271624539519846</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1881,7 +1881,7 @@
         <v>0.026417568879373042</v>
       </c>
       <c r="B26">
-        <v>0.00296997089189144</v>
+        <v>0.0033336976490447629</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1889,7 +1889,7 @@
         <v>0.027474271634547964</v>
       </c>
       <c r="B27">
-        <v>0.0028745674815440023</v>
+        <v>0.003225163491755828</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1897,7 +1897,7 @@
         <v>0.028530974389722887</v>
       </c>
       <c r="B28">
-        <v>0.0027650008306935206</v>
+        <v>0.003100995692084212</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1905,7 +1905,7 @@
         <v>0.029587677144897812</v>
       </c>
       <c r="B29">
-        <v>0.0026408294382028069</v>
+        <v>0.0029606299600289446</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1913,7 +1913,7 @@
         <v>0.030644379900072734</v>
       </c>
       <c r="B30">
-        <v>0.0025018452267861133</v>
+        <v>0.0028038025036486508</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1921,7 +1921,7 @@
         <v>0.031701082655247653</v>
       </c>
       <c r="B31">
-        <v>0.0023487738145634585</v>
+        <v>0.0026314515232403308</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1929,7 +1929,7 @@
         <v>0.032757785410422575</v>
       </c>
       <c r="B32">
-        <v>0.002182574243506302</v>
+        <v>0.0024448157171605778</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1937,7 +1937,7 @@
         <v>0.0338144881655975</v>
       </c>
       <c r="B33">
-        <v>0.0020042055555861047</v>
+        <v>0.0022451337837659869</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1945,7 +1945,7 @@
         <v>0.03487119092077242</v>
       </c>
       <c r="B34">
-        <v>0.0018142465398164921</v>
+        <v>0.0020331559356754096</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1953,7 +1953,7 @@
         <v>0.035927893675947342</v>
       </c>
       <c r="B35">
-        <v>0.001611754973379755</v>
+        <v>0.0018076784425567296</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1961,7 +1961,7 @@
         <v>0.036984596431122257</v>
       </c>
       <c r="B36">
-        <v>0.00139540838050035</v>
+        <v>0.0015670090883400899</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1969,7 +1969,7 @@
         <v>0.03804129918629718</v>
       </c>
       <c r="B37">
-        <v>0.0011638842854027318</v>
+        <v>0.0013094556569556287</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1977,7 +1977,7 @@
         <v>0.0390980019414721</v>
       </c>
       <c r="B38">
-        <v>0.00091492953469699413</v>
+        <v>0.0010321297317343894</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1985,7 +1985,7 @@
         <v>0.040154704696647031</v>
       </c>
       <c r="B39">
-        <v>0.00064256826453577766</v>
+        <v>0.00072735809361101314</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1993,7 +1993,7 @@
         <v>0.041211407451821953</v>
       </c>
       <c r="B40">
-        <v>0.0003398939334573595</v>
+        <v>0.00038627132292104184</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2009,7 +2009,7 @@
         <v>0.042268110206996869</v>
       </c>
       <c r="B42">
-        <v>1.8779977099063261E-17</v>
+        <v>1.8775394381371935E-17</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -2017,7 +2017,7 @@
         <v>0.041211407451821953</v>
       </c>
       <c r="B43">
-        <v>1.5252207211584028E-05</v>
+        <v>-3.1125182252098231E-05</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2025,7 +2025,7 @@
         <v>0.040154704696647031</v>
       </c>
       <c r="B44">
-        <v>4.9039461009128708E-05</v>
+        <v>-3.5750368066106857E-05</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2033,7 +2033,7 @@
         <v>0.0390980019414721</v>
       </c>
       <c r="B45">
-        <v>9.4528155435226525E-05</v>
+        <v>-2.2672041602168792E-05</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2041,7 +2041,7 @@
         <v>0.03804129918629718</v>
       </c>
       <c r="B46">
-        <v>0.00014488468453245114</v>
+        <v>-6.8668702044597328E-07</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2049,7 +2049,7 @@
         <v>0.036984596431122257</v>
       </c>
       <c r="B47">
-        <v>0.00019420342562217062</v>
+        <v>2.2602717782430835E-05</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2057,7 +2057,7 @@
         <v>0.035927893675947342</v>
       </c>
       <c r="B48">
-        <v>0.00024029068914093013</v>
+        <v>4.4367219963955278E-05</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -2065,7 +2065,7 @@
         <v>0.03487119092077242</v>
       </c>
       <c r="B49">
-        <v>0.00028188076880406986</v>
+        <v>6.2971372945152453E-05</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -2073,7 +2073,7 @@
         <v>0.0338144881655975</v>
       </c>
       <c r="B50">
-        <v>0.00031770795832692929</v>
+        <v>7.6779730147047117E-05</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -2081,7 +2081,7 @@
         <v>0.032757785410422575</v>
       </c>
       <c r="B51">
-        <v>0.00034688392792637125</v>
+        <v>8.4642454272095479E-05</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -2089,7 +2089,7 @@
         <v>0.031701082655247653</v>
       </c>
       <c r="B52">
-        <v>0.00037002985382535115</v>
+        <v>8.7352145148478807E-05</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -2097,7 +2097,7 @@
         <v>0.030644379900072734</v>
       </c>
       <c r="B53">
-        <v>0.00038814428874834749</v>
+        <v>8.618701188580974E-05</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -2105,7 +2105,7 @@
         <v>0.029587677144897812</v>
       </c>
       <c r="B54">
-        <v>0.0004022257854198389</v>
+        <v>8.2425263593700819E-05</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -2113,7 +2113,7 @@
         <v>0.028530974389722887</v>
       </c>
       <c r="B55">
-        <v>0.00041303680095867849</v>
+        <v>7.704193956798694E-05</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -2121,7 +2121,7 @@
         <v>0.027474271634547964</v>
       </c>
       <c r="B56">
-        <v>0.00042039541006121817</v>
+        <v>6.9799399849391987E-05</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -2129,7 +2129,7 @@
         <v>0.026417568879373042</v>
       </c>
       <c r="B57">
-        <v>0.00042388359181818442</v>
+        <v>6.0156834664862147E-05</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -2137,7 +2137,7 @@
         <v>0.025360866124198123</v>
       </c>
       <c r="B58">
-        <v>0.00042308332532030372</v>
+        <v>4.7573434241343641E-05</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -2145,7 +2145,7 @@
         <v>0.0243041633690232</v>
       </c>
       <c r="B59">
-        <v>0.0004176269763235566</v>
+        <v>3.1573542894901293E-05</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -2153,7 +2153,7 @@
         <v>0.023247460613848279</v>
       </c>
       <c r="B60">
-        <v>0.00040734845724493867</v>
+        <v>1.1942121298075247E-05</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -2161,7 +2161,7 @@
         <v>0.022190757858673357</v>
       </c>
       <c r="B61">
-        <v>0.00039213206716669951</v>
+        <v>-1.1470715787475714E-05</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -2169,7 +2169,7 @@
         <v>0.021134055103498434</v>
       </c>
       <c r="B62">
-        <v>0.00037186210517108862</v>
+        <v>-3.8814853600092755E-05</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -2177,7 +2177,7 @@
         <v>0.020077352348323516</v>
       </c>
       <c r="B63">
-        <v>0.0003467361760777284</v>
+        <v>-6.9836972664525569E-05</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -2185,7 +2185,7 @@
         <v>0.01902064959314859</v>
       </c>
       <c r="B64">
-        <v>0.00031820510765573188</v>
+        <v>-0.00010267093465115839</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -2193,7 +2193,7 @@
         <v>0.017963946837973671</v>
       </c>
       <c r="B65">
-        <v>0.00028803303341158512</v>
+        <v>-0.0001350473965167838</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -2201,7 +2201,7 @@
         <v>0.016907244082798749</v>
       </c>
       <c r="B66">
-        <v>0.00025798408685177382</v>
+        <v>-0.00016469701521819465</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -2209,7 +2209,7 @@
         <v>0.015850541327623827</v>
       </c>
       <c r="B67">
-        <v>0.00022753742774930873</v>
+        <v>-0.0001922879617202624</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -2217,7 +2217,7 @@
         <v>0.014793838572448906</v>
       </c>
       <c r="B68">
-        <v>0.00018703232094329904</v>
+        <v>-0.000230238463020174</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -2225,7 +2225,7 @@
         <v>0.013737135817273982</v>
       </c>
       <c r="B69">
-        <v>0.00012898291131925685</v>
+        <v>-0.00028817002325606371</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -2233,7 +2233,7 @@
         <v>0.012680433062099062</v>
       </c>
       <c r="B70">
-        <v>6.37427588822084E-05</v>
+        <v>-0.00035276719909753851</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -2241,7 +2241,7 @@
         <v>0.011623730306924139</v>
       </c>
       <c r="B71">
-        <v>2.6001184767747209E-06</v>
+        <v>-0.00040951245251565055</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -2249,7 +2249,7 @@
         <v>0.010567027551749217</v>
       </c>
       <c r="B72">
-        <v>-5.725739081355615E-05</v>
+        <v>-0.00046201681415575794</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -2257,7 +2257,7 @@
         <v>0.0095103247965742949</v>
       </c>
       <c r="B73">
-        <v>-0.00012051923105310986</v>
+        <v>-0.00051630430716458379</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -2265,7 +2265,7 @@
         <v>0.0084536220413993744</v>
       </c>
       <c r="B74">
-        <v>-0.0001852825531363335</v>
+        <v>-0.00056992235602000487</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -2273,7 +2273,7 @@
         <v>0.0073969192862244531</v>
       </c>
       <c r="B75">
-        <v>-0.00024796098634982027</v>
+        <v>-0.00061825346567362946</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -2281,7 +2281,7 @@
         <v>0.0063402165310495308</v>
       </c>
       <c r="B76">
-        <v>-0.00030482638471862671</v>
+        <v>-0.00065649706164084046</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -2289,7 +2289,7 @@
         <v>0.0052835137758746086</v>
       </c>
       <c r="B77">
-        <v>-0.00035242983553107127</v>
+        <v>-0.0006802111716039716</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -2297,7 +2297,7 @@
         <v>0.0042268110206996872</v>
       </c>
       <c r="B78">
-        <v>-0.00038858113439005614</v>
+        <v>-0.00068657131134938385</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -2305,7 +2305,7 @@
         <v>0.0031701082655247654</v>
       </c>
       <c r="B79">
-        <v>-0.00040953044124172715</v>
+        <v>-0.00067074736232096757</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -2313,7 +2313,7 @@
         <v>0.0021134055103498436</v>
       </c>
       <c r="B80">
-        <v>-0.00040868190442244008</v>
+        <v>-0.000624249266478124</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -2321,7 +2321,7 @@
         <v>0.0010567027551749218</v>
       </c>
       <c r="B81">
-        <v>-0.00036979831624264873</v>
+        <v>-0.000526190324008537</v>
       </c>
     </row>
     <row r="82" spans="1:2">
